--- a/data/trans_orig/P16A01-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A01-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>77327</t>
+          <t>77320</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>113607</t>
+          <t>114338</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61820</t>
+          <t>59904</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>95942</t>
+          <t>93619</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,47 +783,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
+          <t>7,12%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>171262</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>147775</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>198252</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>7,3%</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>171262</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>149378</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>200366</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>7,3%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>918116</t>
+          <t>917385</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>954396</t>
+          <t>954403</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1219171</t>
+          <t>1221494</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1253293</t>
+          <t>1255209</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,47 +896,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
+          <t>92,88%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>95,44%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>2158</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2175573</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>2148583</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>2199060</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>92,7%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>95,3%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2158</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>2175573</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>2146469</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>2197457</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>92,7%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80277</t>
+          <t>79185</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>119715</t>
+          <t>116385</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75605</t>
+          <t>76831</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>116197</t>
+          <t>116428</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>165825</t>
+          <t>165116</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>220306</t>
+          <t>220626</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1572679</t>
+          <t>1576009</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1612117</t>
+          <t>1613209</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1471476</t>
+          <t>1471245</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1512068</t>
+          <t>1510842</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3059761</t>
+          <t>3059441</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3114242</t>
+          <t>3114951</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,97%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25313</t>
+          <t>24736</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48589</t>
+          <t>48615</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33851</t>
+          <t>32867</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59685</t>
+          <t>58587</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62932</t>
+          <t>63950</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99462</t>
+          <t>97701</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>502819</t>
+          <t>502793</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>526095</t>
+          <t>526672</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>416727</t>
+          <t>417825</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>442561</t>
+          <t>443545</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>928358</t>
+          <t>930119</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>964888</t>
+          <t>963870</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,78%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>196981</t>
+          <t>198803</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>255794</t>
+          <t>256265</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>187296</t>
+          <t>189238</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>248215</t>
+          <t>247559</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>405507</t>
+          <t>400407</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>490355</t>
+          <t>487562</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3019731</t>
+          <t>3019260</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3078544</t>
+          <t>3076722</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3130982</t>
+          <t>3131638</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3191901</t>
+          <t>3189959</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6164367</t>
+          <t>6167160</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6249215</t>
+          <t>6254315</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89692</t>
+          <t>89513</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>131700</t>
+          <t>128646</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,49 +2351,49 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>9,21%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,24%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>103622</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>85372</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>122903</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>7,78%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>6,41%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
           <t>9,23%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,55%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>103622</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>85165</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>124289</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,78%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>6,4%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>9,33%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>201</t>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>189699</t>
+          <t>184892</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>244367</t>
+          <t>240175</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>840137</t>
+          <t>843191</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>882145</t>
+          <t>882324</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,47 +2464,47 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>90,79%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1144</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1227843</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1208562</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1246093</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>92,22%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
           <t>90,77%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1144</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1227843</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1207176</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1246300</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,22%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>90,67%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2058935</t>
+          <t>2063127</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2113603</t>
+          <t>2118410</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,97%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>142052</t>
+          <t>141078</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>195357</t>
+          <t>191512</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>132291</t>
+          <t>132225</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>180835</t>
+          <t>181750</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>287345</t>
+          <t>288682</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>355580</t>
+          <t>359910</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1764665</t>
+          <t>1768510</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1817970</t>
+          <t>1818944</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1571014</t>
+          <t>1570099</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1619558</t>
+          <t>1619624</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3356291</t>
+          <t>3351961</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3424526</t>
+          <t>3423189</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,22%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33376</t>
+          <t>35498</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65788</t>
+          <t>68048</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25113</t>
+          <t>25251</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49239</t>
+          <t>49210</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65029</t>
+          <t>64918</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>102620</t>
+          <t>105654</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>414544</t>
+          <t>412284</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>446956</t>
+          <t>444834</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>408415</t>
+          <t>408444</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>432541</t>
+          <t>432403</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>835366</t>
+          <t>832332</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>872957</t>
+          <t>873068</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,08%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>288932</t>
+          <t>288083</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>360290</t>
+          <t>358811</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>263549</t>
+          <t>264385</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>326701</t>
+          <t>328642</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>569761</t>
+          <t>569642</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>669880</t>
+          <t>667944</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3051901</t>
+          <t>3053380</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3123259</t>
+          <t>3124108</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3214268</t>
+          <t>3212327</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3277420</t>
+          <t>3276584</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6283280</t>
+          <t>6285216</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6383399</t>
+          <t>6383518</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48957</t>
+          <t>50194</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>78401</t>
+          <t>81584</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55723</t>
+          <t>53584</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91100</t>
+          <t>89115</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>113436</t>
+          <t>112383</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>158412</t>
+          <t>160747</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>675946</t>
+          <t>672763</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>705390</t>
+          <t>704153</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>903560</t>
+          <t>905545</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>938937</t>
+          <t>941076</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1590595</t>
+          <t>1588260</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1635571</t>
+          <t>1636624</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,57%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>135151</t>
+          <t>134523</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>184854</t>
+          <t>183039</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>152657</t>
+          <t>150229</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>204453</t>
+          <t>202622</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>300757</t>
+          <t>300804</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>370901</t>
+          <t>369405</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1891531</t>
+          <t>1893346</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1941234</t>
+          <t>1941862</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1783847</t>
+          <t>1785678</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1835643</t>
+          <t>1838071</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3693784</t>
+          <t>3695280</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3763928</t>
+          <t>3763881</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27501</t>
+          <t>28571</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52678</t>
+          <t>52759</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34086</t>
+          <t>34574</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60963</t>
+          <t>60511</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67677</t>
+          <t>69090</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>106256</t>
+          <t>105668</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>494208</t>
+          <t>494127</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>519385</t>
+          <t>518315</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>488177</t>
+          <t>488629</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>515054</t>
+          <t>514566</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>989771</t>
+          <t>990359</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1028350</t>
+          <t>1026937</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>233595</t>
+          <t>229394</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>297332</t>
+          <t>291825</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>261010</t>
+          <t>258571</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>329677</t>
+          <t>327784</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>507693</t>
+          <t>509886</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>603830</t>
+          <t>601815</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3080286</t>
+          <t>3085793</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3144023</t>
+          <t>3148224</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3202423</t>
+          <t>3204316</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3271090</t>
+          <t>3273529</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6305888</t>
+          <t>6307903</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6402025</t>
+          <t>6399832</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,62%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33498</t>
+          <t>32836</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58511</t>
+          <t>57798</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50736</t>
+          <t>50284</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72511</t>
+          <t>70994</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88029</t>
+          <t>89390</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>122652</t>
+          <t>122347</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>455431</t>
+          <t>456144</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>480444</t>
+          <t>481106</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>679221</t>
+          <t>680738</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>700996</t>
+          <t>701448</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1143021</t>
+          <t>1143326</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1177644</t>
+          <t>1176283</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,94%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89414</t>
+          <t>88216</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>158900</t>
+          <t>159361</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>112456</t>
+          <t>111688</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>183605</t>
+          <t>183489</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>224546</t>
+          <t>222308</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>329214</t>
+          <t>324686</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2131427</t>
+          <t>2130966</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2200913</t>
+          <t>2202111</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2052759</t>
+          <t>2052875</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2123908</t>
+          <t>2124676</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4197477</t>
+          <t>4202005</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4302145</t>
+          <t>4304383</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40409</t>
+          <t>41287</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77102</t>
+          <t>76042</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37753</t>
+          <t>38057</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60155</t>
+          <t>59405</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85853</t>
+          <t>84650</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>128797</t>
+          <t>125911</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>569521</t>
+          <t>570581</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>606214</t>
+          <t>605336</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>600308</t>
+          <t>601058</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>622710</t>
+          <t>622406</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1178289</t>
+          <t>1181175</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1221233</t>
+          <t>1222436</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>176519</t>
+          <t>171959</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>266677</t>
+          <t>266946</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>211784</t>
+          <t>213948</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>293280</t>
+          <t>297209</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>424363</t>
+          <t>418744</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>542774</t>
+          <t>543066</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3184215</t>
+          <t>3183946</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3274373</t>
+          <t>3278933</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3355278</t>
+          <t>3351349</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3436774</t>
+          <t>3434610</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6556676</t>
+          <t>6556384</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6675087</t>
+          <t>6680706</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A01-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A01-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>77320</t>
+          <t>76882</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114338</t>
+          <t>113805</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59904</t>
+          <t>61637</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>93619</t>
+          <t>94412</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>147775</t>
+          <t>146899</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>198252</t>
+          <t>195368</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>917385</t>
+          <t>917918</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>954403</t>
+          <t>954841</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1221494</t>
+          <t>1220701</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1255209</t>
+          <t>1253476</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2148583</t>
+          <t>2151467</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2199060</t>
+          <t>2199936</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,74%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79185</t>
+          <t>79314</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>116385</t>
+          <t>118368</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76831</t>
+          <t>77961</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>116428</t>
+          <t>115564</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>165116</t>
+          <t>165439</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>220626</t>
+          <t>221464</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1576009</t>
+          <t>1574026</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1613209</t>
+          <t>1613080</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1471245</t>
+          <t>1472109</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1510842</t>
+          <t>1509712</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3059441</t>
+          <t>3058603</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3114951</t>
+          <t>3114628</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,96%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24736</t>
+          <t>24221</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48615</t>
+          <t>49435</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32867</t>
+          <t>33081</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58587</t>
+          <t>57800</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63950</t>
+          <t>63479</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97701</t>
+          <t>99050</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>502793</t>
+          <t>501973</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>526672</t>
+          <t>527187</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>417825</t>
+          <t>418612</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>443545</t>
+          <t>443331</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>930119</t>
+          <t>928770</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>963870</t>
+          <t>964341</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,82%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>198803</t>
+          <t>200192</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>256265</t>
+          <t>258625</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>189238</t>
+          <t>190866</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>247559</t>
+          <t>247570</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>400407</t>
+          <t>405828</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>487562</t>
+          <t>486224</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3019260</t>
+          <t>3016900</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3076722</t>
+          <t>3075333</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3131638</t>
+          <t>3131627</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3189959</t>
+          <t>3188331</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6167160</t>
+          <t>6168498</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6254315</t>
+          <t>6248894</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,9%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89513</t>
+          <t>90767</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>128646</t>
+          <t>130335</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>85372</t>
+          <t>83148</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>122903</t>
+          <t>125817</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>184892</t>
+          <t>187107</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>240175</t>
+          <t>241677</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>843191</t>
+          <t>841502</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>882324</t>
+          <t>881070</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1208562</t>
+          <t>1205648</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1246093</t>
+          <t>1248317</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2063127</t>
+          <t>2061625</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2118410</t>
+          <t>2116195</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,88%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>141078</t>
+          <t>139546</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>191512</t>
+          <t>193253</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>132225</t>
+          <t>131807</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>181750</t>
+          <t>182265</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>288682</t>
+          <t>288893</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>359910</t>
+          <t>356665</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1768510</t>
+          <t>1766769</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1818944</t>
+          <t>1820476</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1570099</t>
+          <t>1569584</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1619624</t>
+          <t>1620042</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3351961</t>
+          <t>3355206</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3423189</t>
+          <t>3422978</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35498</t>
+          <t>33203</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68048</t>
+          <t>64688</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25251</t>
+          <t>24785</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49210</t>
+          <t>49557</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64918</t>
+          <t>63419</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105654</t>
+          <t>104297</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>412284</t>
+          <t>415644</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>444834</t>
+          <t>447129</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>408444</t>
+          <t>408097</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>432403</t>
+          <t>432869</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>832332</t>
+          <t>833689</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>873068</t>
+          <t>874567</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,24%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>288083</t>
+          <t>287682</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>358811</t>
+          <t>360846</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>264385</t>
+          <t>261785</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>328642</t>
+          <t>331915</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>569642</t>
+          <t>569777</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>667944</t>
+          <t>666663</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3053380</t>
+          <t>3051345</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3124108</t>
+          <t>3124509</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3212327</t>
+          <t>3209054</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3276584</t>
+          <t>3279184</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6285216</t>
+          <t>6286497</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6383518</t>
+          <t>6383383</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50194</t>
+          <t>48389</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>81584</t>
+          <t>79950</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53584</t>
+          <t>56325</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>89115</t>
+          <t>91454</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>112383</t>
+          <t>112257</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>160747</t>
+          <t>158388</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>672763</t>
+          <t>674397</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>704153</t>
+          <t>705958</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>905545</t>
+          <t>903206</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>941076</t>
+          <t>938335</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1588260</t>
+          <t>1590619</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1636624</t>
+          <t>1636750</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,58%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>134523</t>
+          <t>133690</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>183039</t>
+          <t>185060</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>150229</t>
+          <t>151658</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>202622</t>
+          <t>204625</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>300804</t>
+          <t>298499</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>369405</t>
+          <t>369276</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1893346</t>
+          <t>1891325</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1941862</t>
+          <t>1942695</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1785678</t>
+          <t>1783675</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1838071</t>
+          <t>1836642</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3695280</t>
+          <t>3695409</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3763881</t>
+          <t>3766186</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,66%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28571</t>
+          <t>28273</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52759</t>
+          <t>55256</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34574</t>
+          <t>35008</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60511</t>
+          <t>60767</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69090</t>
+          <t>67660</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105668</t>
+          <t>105486</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>494127</t>
+          <t>491630</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>518315</t>
+          <t>518613</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>488629</t>
+          <t>488373</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>514566</t>
+          <t>514132</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>990359</t>
+          <t>990541</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1026937</t>
+          <t>1028367</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,83%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>229394</t>
+          <t>231231</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>291825</t>
+          <t>294712</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>258571</t>
+          <t>259690</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>327784</t>
+          <t>327561</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>509886</t>
+          <t>507048</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>601815</t>
+          <t>597849</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3085793</t>
+          <t>3082906</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3148224</t>
+          <t>3146387</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3204316</t>
+          <t>3204539</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3273529</t>
+          <t>3272410</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6307903</t>
+          <t>6311869</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6399832</t>
+          <t>6402670</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,66%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>44093</t>
+          <t>46029</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32836</t>
+          <t>34824</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57798</t>
+          <t>59718</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>60520</t>
+          <t>66663</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50284</t>
+          <t>55010</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>70994</t>
+          <t>79574</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>104613</t>
+          <t>112691</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>89390</t>
+          <t>96974</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>122347</t>
+          <t>131191</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>469849</t>
+          <t>531513</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>456144</t>
+          <t>517824</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>481106</t>
+          <t>542718</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>691212</t>
+          <t>753122</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>680738</t>
+          <t>740211</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>701448</t>
+          <t>764775</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1161060</t>
+          <t>1284636</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1143326</t>
+          <t>1266136</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1176283</t>
+          <t>1300353</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,06%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>751732</t>
+          <t>819785</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>751732</t>
+          <t>819785</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>751732</t>
+          <t>819785</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1265673</t>
+          <t>1397327</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1265673</t>
+          <t>1397327</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1265673</t>
+          <t>1397327</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>128432</t>
+          <t>146949</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88216</t>
+          <t>122305</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>159361</t>
+          <t>177324</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>152292</t>
+          <t>166252</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>111688</t>
+          <t>144148</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>183489</t>
+          <t>192084</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>280723</t>
+          <t>313201</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>222308</t>
+          <t>277830</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>324686</t>
+          <t>347833</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2161895</t>
+          <t>2083617</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2130966</t>
+          <t>2053242</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2202111</t>
+          <t>2108261</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2084072</t>
+          <t>2003690</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2052875</t>
+          <t>1977858</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2124676</t>
+          <t>2025794</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4245968</t>
+          <t>4087307</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4202005</t>
+          <t>4052675</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4304383</t>
+          <t>4122678</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2236364</t>
+          <t>2169942</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2236364</t>
+          <t>2169942</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2236364</t>
+          <t>2169942</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4526691</t>
+          <t>4400508</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4526691</t>
+          <t>4400508</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4526691</t>
+          <t>4400508</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>56107</t>
+          <t>60691</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41287</t>
+          <t>44550</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76042</t>
+          <t>79728</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>47542</t>
+          <t>54146</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38057</t>
+          <t>42850</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59405</t>
+          <t>67414</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>103648</t>
+          <t>114838</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84650</t>
+          <t>94204</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125911</t>
+          <t>140025</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>590516</t>
+          <t>650896</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>570581</t>
+          <t>631859</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>605336</t>
+          <t>667037</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>612921</t>
+          <t>680731</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>601058</t>
+          <t>667463</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>622406</t>
+          <t>692027</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1203438</t>
+          <t>1331626</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1181175</t>
+          <t>1306439</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1222436</t>
+          <t>1352260</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,49%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>228631</t>
+          <t>253669</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>171959</t>
+          <t>220039</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>266946</t>
+          <t>288964</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,67 +6601,67 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>260353</t>
+          <t>287061</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>213948</t>
+          <t>260369</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>297209</t>
+          <t>318930</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
+          <t>8,56%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>540730</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>500862</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>590106</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>7,46%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>6,91%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>8,15%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>488985</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>418744</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>543066</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>6,89%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>5,9%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3222261</t>
+          <t>3266026</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3183946</t>
+          <t>3230731</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3278933</t>
+          <t>3299656</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,67 +6714,67 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3388205</t>
+          <t>3437543</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3351349</t>
+          <t>3405674</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3434610</t>
+          <t>3464235</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>91,44%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>93,01%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>8054</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>6703569</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>6654193</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>6743437</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>92,54%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>91,85%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>94,14%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>8054</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>6610465</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>6556384</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>6680706</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>93,11%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>92,35%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,09%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3450892</t>
+          <t>3519695</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3450892</t>
+          <t>3519695</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3450892</t>
+          <t>3519695</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3648558</t>
+          <t>3724604</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3648558</t>
+          <t>3724604</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3648558</t>
+          <t>3724604</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7099450</t>
+          <t>7244299</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7099450</t>
+          <t>7244299</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7099450</t>
+          <t>7244299</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
